--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_834_Tanzania.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_834_Tanzania.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R338b9d0d91dc4b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd4f8ec19218a40e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R264c002e72fa4347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2e75376151b34c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R31d604fcd9694a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R375a0aec3bc14435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R37972a65b26047ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6cde7cacc8a244b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R589c83ccba2c440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rad42d6bd5a0e4c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R05a699512c8a477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R418af877d2104128"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ834CommercialTable" displayName="EEZ834CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ834CommercialTable" displayName="EEZ834CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ834FunctionalTable" displayName="EEZ834FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ834FunctionalTable" displayName="EEZ834FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ834ValidationTable" displayName="EEZ834ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ834ValidationTable" displayName="EEZ834ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8198,7 +8152,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21407fa054db404f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d11075a76ac4196"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8208,20 +8162,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8229,606 +8173,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.4083623428</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.77616239495518</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.4083623428</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$113,A2,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>89.33994622439715</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>89.33994622439715</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5655.365125318001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.7114413791107292</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>51.45663463736621</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5655.365125318001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>52.97082739489261</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$113,A3,'Species'!$U$2:$U$113))</x:f>
-        <x:v>299569.3699083151</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.7114413791107292</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>51.45663463736621</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>291006.05699439114</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8563.312913923932</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0294265796470654</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.029426579647065496</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>616.8163892366001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.388905781014444</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2448.531981984129</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>616.8163892366001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2452.3910194701816</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$113,A4,'Species'!$U$2:$U$113))</x:f>
-        <x:v>1512674.973625862</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.388905781014444</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2448.531981984129</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1510294.6560577864</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2380.3175680756103</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0015760617032763</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0015760617032763542</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10388.472747218699</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.944829524005163</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>88.07030979307797</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10388.472747218699</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>206.34262695602214</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$113,A5,'Species'!$U$2:$U$113))</x:f>
-        <x:v>2143584.7567221504</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.944829524005163</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>88.07030979307797</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>914916.0131244985</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1228668.7435976518</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.342930636224922</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.3429306362249218</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2607.8602198</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2607.8602198</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$113,A6,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>32831.01501113343</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>32831.01501113343</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>24459.176766261706</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.508205539722924</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>322.2593596009451</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>24459.176766261706</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>357.8169953894081</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$113,A7,'Species'!$U$2:$U$113))</x:f>
-        <x:v>8751909.140202181</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.508205539722924</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>322.2593596009451</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7882198.641061813</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>869710.4991403688</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.110338566527576</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1103385665275761</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>62346.931650147104</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6366590815319837</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>433.1707085764617</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>62346.931650147104</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>814.2777820787046</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$113,A8,'Species'!$U$2:$U$113))</x:f>
-        <x:v>50767721.22349437</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6366590815319837</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>433.1707085764617</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>27006864.56046245</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>23760856.663031925</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8798080432416202</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8798080432416201</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.902224841</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.902224841</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$113,A9,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>716.6626652759254</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>716.6626652759254</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>14866.5255148622</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.037793368003372</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1090.921166018436</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>14866.5255148622</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1351.942242027464</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$113,A10,'Species'!$U$2:$U$113))</x:f>
-        <x:v>20098683.835721303</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.037793368003372</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1090.921166018436</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>16218207.3493163</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3880476.486405002</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2392666712679925</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.23926667126799242</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8572.772211285499</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.464142284667899</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2911.6708908766927</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8572.772211285499</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2943.057999086956</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$113,A11,'Species'!$U$2:$U$113))</x:f>
-        <x:v>25230165.83077416</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.464142284667899</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2911.6708908766927</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>24961091.301716603</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>269074.5290575549</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.010779758216703</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.010779758216703062</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree23e15b8c80413e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b82e6765189411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8838,20 +8388,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8859,1146 +8399,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12421.772023364201</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6175025387770496</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>414.4790069715905</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12421.772023364201</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>431.83597658453516</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$113,A2,'Species'!$U$2:$U$113))</x:f>
-        <x:v>5364168.052619937</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6175025387770496</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>414.4790069715905</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>5148563.733071478</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>215604.3195484588</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0418765952460758</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0418765952460757</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9.9112624969</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9.9112624969</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.62277660168379</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$113,A3,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>313.42163978011536</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>313.42163978011536</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4031.8227799422</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.389857264659674</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2453.9022829590167</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4031.8227799422</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2455.0884104103975</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$113,A4,'Species'!$U$2:$U$113))</x:f>
-        <x:v>9898481.379864726</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.389857264659674</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2453.9022829590167</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>9893699.124186335</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4782.255678391084</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.000483363767016</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0004833637670161493</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>242.1682715694</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.889041313251248</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>774.5354737483113</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>242.1682715694</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>775.0884615341583</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$113,A5,'Species'!$U$2:$U$113))</x:f>
-        <x:v>187701.8330431125</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.889041313251248</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>774.5354737483113</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>187567.91694681495</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>133.9160962975584</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0007139605668038</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0007139605668038124</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>21855.1036328761</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.23484380980036</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1717.2906675655424</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>21855.1036328761</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1985.2388353521885</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$113,A6,'Species'!$U$2:$U$113))</x:f>
-        <x:v>43387600.48263233</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.23484380980036</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1717.2906675655424</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>37531565.50741591</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>5856034.9752164185</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.156029595249879</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.15602959524987883</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4629.859479848</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4629.859479848</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$113,A7,'Species'!$U$2:$U$113))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2429784.794932363</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>2429784.794932363</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>332.03313078</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9865686454533815</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>969.54650564702</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>332.03313078</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>971.6534701246086</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$113,A8,'Species'!$U$2:$U$113))</x:f>
-        <x:v>322621.143718725</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9865686454533815</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>969.54650564702</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>321921.561706789</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>699.5820119359996</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.002173144315736</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0021731443157361092</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>10236.6660350142</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.181525578515132</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1518.8873968644477</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>10236.6660350142</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1726.0403905288124</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$113,A9,'Species'!$U$2:$U$113))</x:f>
-        <x:v>17668899.040788937</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.181525578515132</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1518.8873968644477</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>15548343.026493425</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2120556.014295513</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.136384694541548</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.13638469454154795</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>107.662744298</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.938879549075713</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>86.8719457830414</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>107.662744298</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>108.48258703414787</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$113,A10,'Species'!$U$2:$U$113))</x:f>
-        <x:v>11679.533028642993</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.938879549075713</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>86.8719457830414</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>9352.872085509305</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2326.6609431336874</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.248764328418268</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.24876432841826795</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.9131543498999999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7326796479185234</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>540.3555891262888</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.9131543498999999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>660.5444231223763</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$113,A11,'Species'!$U$2:$U$113))</x:f>
-        <x:v>603.179013276384</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7326796479185234</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>540.3555891262888</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>493.4280567034477</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>109.75095657293633</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2224254480099357</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.22242544800993574</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>9449.4361102412</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.401827740919279</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>252.24800545366</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>9449.4361102412</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>258.5428004768467</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$113,A12,'Species'!$U$2:$U$113))</x:f>
-        <x:v>2443083.674868801</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.401827740919279</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>252.24800545366</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2383601.411470134</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>59482.26339866733</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0249547861116513</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0249547861116513</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>15112.836007707301</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.661106043250928</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>458.25376653084805</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>15112.836007707301</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>815.2634798631519</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$113,A13,'Species'!$U$2:$U$113))</x:f>
-        <x:v>12320943.274244599</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.661106043250928</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>458.25376653084805</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>6925514.023494896</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>5395429.2507497035</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.7790655296409248</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7790655296409249</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>20816.3421201231</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.313551914414621</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>205.85049440763012</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>20816.3421201231</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>386.6739422348537</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$113,A14,'Species'!$U$2:$U$113))</x:f>
-        <x:v>8049137.070497432</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.313551914414621</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>205.85049440763012</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4285054.317185716</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>3764082.753311716</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.8784212461941072</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.8784212461941073</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>2607.945303301</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.099996737527398</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.589159546299424</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>2607.945303301</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.589169644235476</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$113,A15,'Species'!$U$2:$U$113))</x:f>
-        <x:v>32831.86584614343</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.099996737527398</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.589159546299424</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>32831.83951127853</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0.026334864902310073</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0000008021135975</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>8.021135974809883e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5547.702381020001</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.707027548689631</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>50.936318056999994</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5547.702381020001</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>51.89352584316907</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$113,A16,'Species'!$U$2:$U$113))</x:f>
-        <x:v>287889.836879672</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.707027548689631</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>50.936318056999994</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>282579.5329652109</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>5310.30391446111</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0187922453503202</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.018792245350320102</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1904.8654798947998</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1402929704362808</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>138.13157712964136</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1904.8654798947998</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>144.52918010379523</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$113,A17,'Species'!$U$2:$U$113))</x:f>
-        <x:v>275308.64601721783</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1402929704362808</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>138.13157712964136</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>263122.07295767986</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>12186.573059537972</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.046315282190324</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.046315282190324034</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>7780.312874288799</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.503438876347737</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>318.74169393821506</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>7780.312874288799</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>392.46781125446006</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$113,A18,'Species'!$U$2:$U$113))</x:f>
-        <x:v>3053522.364647022</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.503438876347737</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>318.74169393821506</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>2479910.104920115</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>573612.2597269071</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.231303650317351</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.23130365031735087</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>10687.7874931304</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.8629255589596565</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>72.93324869704892</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>10687.7874931304</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>87.37642195064903</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$113,A19,'Species'!$U$2:$U$113))</x:f>
-        <x:v>933860.6297186312</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.8629255589596565</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>72.93324869704892</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>779495.0632576885</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>154365.56646094262</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1980327698495146</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.19803276984951454</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1123.2745378315</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.2394457577743</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>173.55844794485336</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1123.2745378315</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>584.7554879253385</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$113,A20,'Species'!$U$2:$U$113))</x:f>
-        <x:v>656840.950443768</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.2394457577743</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>173.55844794485336</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>194953.7854020076</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>461887.1650417603</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>3.3692136271646045</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>2.369213627164604</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>616.8163892366001</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.388905781014444</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>2448.531981984129</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>616.8163892366001</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>2452.3910194701816</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$113,A21,'Species'!$U$2:$U$113))</x:f>
-        <x:v>1512674.973625862</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.388905781014444</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>2448.531981984129</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1510294.6560577864</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>2380.3175680756103</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0015760617032763</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0015760617032763542</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd57da01a2804ff2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59526d2b0e944b28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10173,7 +8969,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10272,7 +9068,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>108837946.14807098</x:v>
+        <x:v>78818215.59635648</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10286,7 +9082,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>108837946.14807098</x:v>
+        <x:v>90208962.19375764</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10300,7 +9096,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-30019730.551714495</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10314,7 +9110,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-18628983.954313338</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10325,9 +9121,9 @@
         <x:v>EEZ_834</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10339,47 +9135,19 @@
         <x:v>EEZ_834</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_834</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_834</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27ab00fc2ef94406"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f9c8b2f6b674f93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10426,7 +9194,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
